--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104623_W19.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104623_W19.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7369</v>
+        <v>8.305899999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5844</v>
+        <v>6.5834</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1524</v>
+        <v>1.7225</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.5044</v>
+        <v>-0.5112</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5524</v>
+        <v>-0.5651</v>
       </c>
       <c r="I2" t="n">
-        <v>0.048</v>
+        <v>0.0539</v>
       </c>
       <c r="J2" t="n">
-        <v>0.494</v>
+        <v>0.4605</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0631</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9984</v>
+        <v>-0.9717</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4981</v>
+        <v>1.0998</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4506</v>
+        <v>0.6151</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0475</v>
+        <v>0.4846</v>
       </c>
       <c r="V2" t="n">
-        <v>8.4199</v>
+        <v>8.4003</v>
       </c>
       <c r="W2" t="n">
-        <v>7.8094</v>
+        <v>7.7841</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2302</v>
+        <v>2.4398</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8499</v>
+        <v>4.1531</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6196</v>
+        <v>-1.7133</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3471</v>
+        <v>-0.3694</v>
       </c>
       <c r="H3" t="n">
-        <v>0.394</v>
+        <v>0.3881</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7411</v>
+        <v>-0.7574</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8486</v>
+        <v>0.8051</v>
       </c>
       <c r="K3" t="n">
-        <v>1.198</v>
+        <v>1.1786</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3494</v>
+        <v>-0.3735</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1957</v>
+        <v>-1.1745</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>0.963</v>
+        <v>1.1962</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3357</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6273</v>
+        <v>0.5021</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W3" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1866</v>
+        <v>1.8163</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3994</v>
+        <v>1.9158</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2129</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9751</v>
+        <v>0.9764</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1963</v>
+        <v>1.1921</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2212</v>
+        <v>-0.2158</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7109</v>
+        <v>0.701</v>
       </c>
       <c r="K4" t="n">
-        <v>0.599</v>
+        <v>0.5893</v>
       </c>
       <c r="L4" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2641</v>
+        <v>0.2754</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.6028</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6917</v>
+        <v>0.3148</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5958</v>
+        <v>0.1253</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0959</v>
+        <v>0.1895</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>K. KUATH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6966</v>
+        <v>0.999</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3018</v>
+        <v>-0.673</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.6053</v>
+        <v>1.6721</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0316</v>
+        <v>2.4797</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0187</v>
+        <v>1.2522</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0129</v>
+        <v>1.2275</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5472</v>
+        <v>1.7334</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9902</v>
+        <v>1.1376</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5958</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5788</v>
+        <v>0.7463</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0089</v>
+        <v>0.1146</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5699</v>
+        <v>0.6317</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6805</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-2.5039</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>4.9362</v>
+        <v>0.1127</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4993</v>
+        <v>0.0975</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4369</v>
+        <v>0.0152</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.8885</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6105</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. KUATH</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6111</v>
+        <v>0.3114</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8943</v>
+        <v>2.0215</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5054</v>
+        <v>-1.7101</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4786</v>
+        <v>2.8897</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2525</v>
+        <v>0.0983</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2262</v>
+        <v>2.7915</v>
       </c>
       <c r="J6" t="n">
-        <v>1.74</v>
+        <v>4.6931</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1429</v>
+        <v>0.7165</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5971</v>
+        <v>3.9767</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7387</v>
+        <v>-1.8034</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1096</v>
+        <v>-0.6182</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6291</v>
+        <v>-1.1852</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5878</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.4952</v>
+        <v>-3.4145</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2798</v>
+        <v>1.2623</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1391</v>
+        <v>0.7428</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1406</v>
+        <v>0.5195</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>L. LABEYRIE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1294</v>
+        <v>0.2589</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5945</v>
+        <v>0.0487</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4651</v>
+        <v>0.2102</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9033</v>
+        <v>0.1579</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1099</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7935</v>
+        <v>0.1579</v>
       </c>
       <c r="J7" t="n">
-        <v>4.7308</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7406</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3.9902</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8275</v>
+        <v>0.1579</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6308</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1967</v>
+        <v>0.1579</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.0415</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0673</v>
+        <v>0.101</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2662</v>
+        <v>0.0487</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8012</v>
+        <v>0.0523</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. LABEYRIE</t>
+          <t>Z. SAMAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1086</v>
+        <v>-1.274</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0696</v>
+        <v>-0.0224</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1781</v>
+        <v>-1.2516</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1573</v>
+        <v>1.5448</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.8758</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1573</v>
+        <v>0.669</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.1576</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.1204</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.0372</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1573</v>
+        <v>0.3871</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.2446</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1573</v>
+        <v>0.6317</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0487</v>
+        <v>0.043</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0696</v>
+        <v>-0.0419</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0209</v>
+        <v>0.0849</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Z. SAMAR</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5506</v>
+        <v>-1.828</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2495</v>
+        <v>1.389</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3011</v>
+        <v>-3.217</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5393</v>
+        <v>-1.0267</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8729</v>
+        <v>-0.02</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6664</v>
+        <v>-1.0067</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1629</v>
+        <v>1.5227</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1256</v>
+        <v>0.9718</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3764</v>
+        <v>-2.5494</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2526</v>
+        <v>-0.9918</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6291</v>
+        <v>-1.5576</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2241</v>
+        <v>2.4005</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2782</v>
+        <v>1.6207</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0541</v>
+        <v>0.7798</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1853</v>
+        <v>-3.8846</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.6162</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1853</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.51</v>
+        <v>-2.2488</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9453</v>
+        <v>-1.6208</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5647</v>
+        <v>-0.628</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.7771</v>
+        <v>-4.7773</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0982</v>
+        <v>-2.0913</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.6789</v>
+        <v>-2.6861</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.3655</v>
+        <v>-3.3884</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4515</v>
+        <v>-1.4586</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.914</v>
+        <v>-1.9298</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4116</v>
+        <v>-1.389</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0402</v>
+        <v>0.3009</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5383</v>
+        <v>-0.1838</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5786</v>
+        <v>0.4846</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2243</v>
+        <v>-4.405</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7168</v>
+        <v>-1.2165</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5075</v>
+        <v>-3.1885</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.4053</v>
+        <v>-4.4036</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.1125</v>
+        <v>-3.1106</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2928</v>
+        <v>-1.293</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4133</v>
+        <v>-1.4369</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.6318</v>
+        <v>-1.645</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2185</v>
+        <v>0.2081</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.992</v>
+        <v>-2.9667</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4807</v>
+        <v>-1.4656</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5931</v>
+        <v>0.4052</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9648</v>
+        <v>0.4967</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3717</v>
+        <v>-0.0915</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8094</v>
+        <v>-4.7712</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.722</v>
+        <v>-3.7576</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0874</v>
+        <v>-1.0136</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.0654</v>
+        <v>-5.0671</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.896</v>
+        <v>-1.8956</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.1693</v>
+        <v>-3.1715</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.228</v>
+        <v>-2.2612</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.0603</v>
+        <v>-1.0762</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1676</v>
+        <v>-1.185</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.8374</v>
+        <v>-2.8059</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8357</v>
+        <v>-0.8194</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.0017</v>
+        <v>-1.9865</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5754</v>
+        <v>1.613</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0011</v>
+        <v>1.0075</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5743</v>
+        <v>0.6055</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3948999999999989</v>
+        <v>-0.3957000000000006</v>
       </c>
       <c r="E13" t="n">
-        <v>9.132500000000002</v>
+        <v>8.821199999999997</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.527700000000001</v>
+        <v>-9.216800000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.077300000000001</v>
+        <v>-8.1068</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.852199999999999</v>
+        <v>-3.8761</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.2248</v>
+        <v>-4.2307</v>
       </c>
       <c r="J13" t="n">
-        <v>4.227600000000001</v>
+        <v>3.986899999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5896</v>
+        <v>1.444</v>
       </c>
       <c r="L13" t="n">
-        <v>2.638100000000001</v>
+        <v>2.543</v>
       </c>
       <c r="M13" t="n">
-        <v>-12.3049</v>
+        <v>-12.0939</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.4418</v>
+        <v>-5.3201</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.8629</v>
+        <v>-6.773899999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1341</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.7442</v>
+        <v>-14.796</v>
       </c>
       <c r="R13" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S13" t="n">
-        <v>8.816199999999998</v>
+        <v>8.849400000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>5.1871</v>
+        <v>5.2227</v>
       </c>
       <c r="U13" t="n">
-        <v>3.6294</v>
+        <v>3.6265</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0001000000000010992</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="W13" t="n">
-        <v>14.462</v>
+        <v>14.4072</v>
       </c>
       <c r="X13" t="n">
-        <v>-14.4619</v>
+        <v>-14.4071</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.5006</v>
+        <v>8.518700000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>7.4581</v>
+        <v>7.1889</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0425</v>
+        <v>1.3298</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1717</v>
+        <v>2.1864</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4284</v>
+        <v>0.4389</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7433</v>
+        <v>1.7475</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4424</v>
+        <v>2.4249</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1314</v>
+        <v>0.1239</v>
       </c>
       <c r="L14" t="n">
-        <v>2.3109</v>
+        <v>2.301</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2707</v>
+        <v>-0.2386</v>
       </c>
       <c r="N14" t="n">
-        <v>0.297</v>
+        <v>0.3149</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9491000000000001</v>
+        <v>-0.9361</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2208</v>
+        <v>-0.4558</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.4804</v>
       </c>
       <c r="V14" t="n">
-        <v>5.4633</v>
+        <v>5.4474</v>
       </c>
       <c r="W14" t="n">
-        <v>5.4633</v>
+        <v>5.4474</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6161</v>
+        <v>2.7795</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0774</v>
+        <v>4.5759</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4613</v>
+        <v>-1.7965</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0434</v>
+        <v>3.0445</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0807</v>
+        <v>3.0817</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0373</v>
+        <v>-0.0372</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8577</v>
+        <v>3.8306</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6019</v>
+        <v>3.5853</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2558</v>
+        <v>0.2453</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8143</v>
+        <v>-0.7861</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5212</v>
+        <v>-0.5036</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9224</v>
+        <v>-0.7689</v>
       </c>
       <c r="T15" t="n">
-        <v>0.127</v>
+        <v>-0.3441</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0495</v>
+        <v>-0.4248</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3197</v>
+        <v>2.2986</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0781</v>
+        <v>1.7928</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2416</v>
+        <v>0.5058</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6738</v>
+        <v>0.6722</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1459</v>
+        <v>0.1356</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5278</v>
+        <v>0.5367</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4808</v>
+        <v>0.453</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3401</v>
+        <v>-0.3662</v>
       </c>
       <c r="L16" t="n">
-        <v>0.821</v>
+        <v>0.8192</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1929</v>
+        <v>0.2192</v>
       </c>
       <c r="N16" t="n">
-        <v>0.486</v>
+        <v>0.5018</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>0.075</v>
+        <v>0.0604</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2662</v>
+        <v>0.0322</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1912</v>
+        <v>0.0283</v>
       </c>
       <c r="V16" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W16" t="n">
-        <v>3.5994</v>
+        <v>3.584</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.5748</v>
+        <v>-1.5628</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2694</v>
+        <v>1.9615</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2887</v>
+        <v>1.5933</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0193</v>
+        <v>0.3682</v>
       </c>
       <c r="G17" t="n">
-        <v>3.7799</v>
+        <v>3.779</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1703</v>
+        <v>-0.1668</v>
       </c>
       <c r="I17" t="n">
-        <v>3.9503</v>
+        <v>3.9458</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7679</v>
+        <v>3.7306</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5928</v>
+        <v>-0.6108</v>
       </c>
       <c r="L17" t="n">
-        <v>4.3606</v>
+        <v>4.3414</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0121</v>
+        <v>0.0484</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4224</v>
+        <v>0.444</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4104</v>
+        <v>-0.3956</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.0569</v>
+        <v>-1.3623</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0767</v>
+        <v>-0.7229</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9802</v>
+        <v>-0.6394</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2541</v>
+        <v>0.5952</v>
       </c>
       <c r="E18" t="n">
-        <v>0.782</v>
+        <v>0.88</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5279</v>
+        <v>-0.2847</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7537</v>
+        <v>1.7578</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3939</v>
+        <v>1.3957</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3599</v>
+        <v>0.3621</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8568</v>
+        <v>1.8429</v>
       </c>
       <c r="K18" t="n">
-        <v>2.0087</v>
+        <v>1.9995</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.103</v>
+        <v>-0.0851</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7265</v>
+        <v>-0.3902</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4869</v>
+        <v>-0.3695</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2395</v>
+        <v>-0.0207</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0118</v>
+        <v>-0.9528</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.14</v>
+        <v>-0.1522</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8718</v>
+        <v>-0.8006</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5303</v>
+        <v>-0.5324</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0028</v>
+        <v>0.0056</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5331</v>
+        <v>-0.538</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1382</v>
+        <v>0.1266</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5541</v>
+        <v>0.5516</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4159</v>
+        <v>-0.4249</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6685</v>
+        <v>-0.659</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5513</v>
+        <v>-0.546</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7083</v>
+        <v>-0.648</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2782</v>
+        <v>-0.2788</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4301</v>
+        <v>-0.3692</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3005</v>
+        <v>-1.0069</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.341</v>
+        <v>-0.4985</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9595</v>
+        <v>-0.5084</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5321</v>
+        <v>-0.5352</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1659</v>
+        <v>1.1661</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.698</v>
+        <v>-1.7013</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8713</v>
+        <v>0.8377</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2153</v>
+        <v>1.1958</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.344</v>
+        <v>-0.3581</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4034</v>
+        <v>-1.3729</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0494</v>
+        <v>-0.0298</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5831</v>
+        <v>-0.2927</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0121</v>
+        <v>-0.1282</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.571</v>
+        <v>-0.1645</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0659</v>
+        <v>-2.4733</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.465</v>
+        <v>-3.158</v>
       </c>
       <c r="F21" t="n">
-        <v>0.399</v>
+        <v>0.6847</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6959</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6262</v>
+        <v>-0.6261</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3221</v>
+        <v>1.3213</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1848</v>
+        <v>-0.2123</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.1123</v>
+        <v>-1.1279</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9275</v>
+        <v>0.9156</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8806</v>
+        <v>0.9074</v>
       </c>
       <c r="N21" t="n">
-        <v>0.486</v>
+        <v>0.5018</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5615</v>
+        <v>-0.9604</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9043</v>
+        <v>-0.5508</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6572</v>
+        <v>-0.4096</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1135</v>
+        <v>-2.8278</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6723</v>
+        <v>-0.5728</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4412</v>
+        <v>-2.255</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.231</v>
+        <v>-1.2252</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1515</v>
+        <v>-1.153</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.283</v>
+        <v>-0.294</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6927</v>
+        <v>0.6895</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.9756</v>
+        <v>-0.9835</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.948</v>
+        <v>-0.9312</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6291</v>
+        <v>-0.3553</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3478</v>
+        <v>-0.2301</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2813</v>
+        <v>-0.1253</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.073</v>
+        <v>-6.1282</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5383</v>
+        <v>-2.4328</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.5347</v>
+        <v>-3.6954</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7478</v>
+        <v>-1.7354</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4892</v>
+        <v>-1.4824</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2585</v>
+        <v>-0.253</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6425</v>
+        <v>-0.6462</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7171</v>
+        <v>-0.7207</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1053</v>
+        <v>-1.0891</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7543</v>
+        <v>-0.8269</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6956</v>
+        <v>-0.5786</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0587</v>
+        <v>-0.2483</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.1173</v>
+        <v>-3.1107</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3951999999999991</v>
+        <v>2.764500000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>9.527699999999999</v>
+        <v>9.2166</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.1326</v>
+        <v>-6.4521</v>
       </c>
       <c r="G24" t="n">
-        <v>8.077199999999999</v>
+        <v>8.106799999999998</v>
       </c>
       <c r="H24" t="n">
-        <v>3.852399999999999</v>
+        <v>3.8761</v>
       </c>
       <c r="I24" t="n">
-        <v>4.225</v>
+        <v>4.2309</v>
       </c>
       <c r="J24" t="n">
-        <v>12.3048</v>
+        <v>12.0938</v>
       </c>
       <c r="K24" t="n">
-        <v>5.441800000000001</v>
+        <v>5.319999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>6.8629</v>
+        <v>6.7739</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.2276</v>
+        <v>-3.987</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5896</v>
+        <v>-1.444</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.638</v>
+        <v>-2.5431</v>
       </c>
       <c r="P24" t="n">
-        <v>1.134</v>
+        <v>1.138</v>
       </c>
       <c r="Q24" t="n">
-        <v>-13.61</v>
+        <v>-13.6579</v>
       </c>
       <c r="R24" t="n">
-        <v>14.7441</v>
+        <v>14.7961</v>
       </c>
       <c r="S24" t="n">
-        <v>-8.8162</v>
+        <v>-6.480399999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.6292</v>
+        <v>-3.6266</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.187</v>
+        <v>-2.8539</v>
       </c>
       <c r="V24" t="n">
-        <v>-9.999999999887876e-05</v>
+        <v>-1.332267629550188e-15</v>
       </c>
       <c r="W24" t="n">
-        <v>14.4619</v>
+        <v>14.4074</v>
       </c>
       <c r="X24" t="n">
-        <v>-14.462</v>
+        <v>-14.4072</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104623_W19.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104623_W19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-14.4071</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.5628</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104623_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-14.4072</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
